--- a/revisao/Dietetica-MTC-revisao.xlsx
+++ b/revisao/Dietetica-MTC-revisao.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3008" uniqueCount="1274">
   <si>
     <t>REVISÃO DA ORIENTAÇÃO ALIMENTAR SEGUNDO A MTC</t>
   </si>
@@ -1233,6 +1233,9 @@
     <t>Aveia</t>
   </si>
   <si>
+    <t>Fresco</t>
+  </si>
+  <si>
     <t>BP E C</t>
   </si>
   <si>
@@ -1257,9 +1260,6 @@
     <t>Painço (milheto)</t>
   </si>
   <si>
-    <t>Fresco</t>
-  </si>
-  <si>
     <t>doce salgado</t>
   </si>
   <si>
@@ -1308,6 +1308,9 @@
     <t>Move o Qi; Ajuda a digestão / dissolve alimentos retidos</t>
   </si>
   <si>
+    <t>Atenção: Pesado para má digestão e vertigens; à noite pode tirar o sono.</t>
+  </si>
+  <si>
     <t>quinoa</t>
   </si>
   <si>
@@ -1368,6 +1371,9 @@
     <t>Drena a umidade; Diurético; Refresca / clareia o calor</t>
   </si>
   <si>
+    <t>Atenção: Não indicado para pessoas muito magras.</t>
+  </si>
+  <si>
     <t>feijao-preto</t>
   </si>
   <si>
@@ -1422,6 +1428,9 @@
     <t>Refresca / clareia o calor; Nutre o Yin; Umedece a secura</t>
   </si>
   <si>
+    <t>Atenção: Evitar na espermatorreia.</t>
+  </si>
+  <si>
     <t>grao-de-bico</t>
   </si>
   <si>
@@ -1560,6 +1569,9 @@
     <t>Refresca / clareia o calor; Diurético; Umedece a secura</t>
   </si>
   <si>
+    <t>Atenção: Com moderação; evitar com catarro, dor abdominal ou diarreia.</t>
+  </si>
+  <si>
     <t>tomate</t>
   </si>
   <si>
@@ -1572,6 +1584,9 @@
     <t>Refresca / clareia o calor; Nutre o Yin; Ajuda a digestão / dissolve alimentos retidos</t>
   </si>
   <si>
+    <t>Atenção: Com moderação, não todo dia: cru no verão, cozido no outono.</t>
+  </si>
+  <si>
     <t>berinjela</t>
   </si>
   <si>
@@ -1605,6 +1620,9 @@
     <t>E IG</t>
   </si>
   <si>
+    <t>Atenção: Em excesso turva a visão; evitar com doença nos olhos.</t>
+  </si>
+  <si>
     <t>agriao</t>
   </si>
   <si>
@@ -1647,6 +1665,9 @@
     <t>Nutre o Sangue (Xue); Nutre o Yin; Umedece os intestinos (laxante suave); Refresca / clareia o calor</t>
   </si>
   <si>
+    <t>Atenção: Evitar com diarreia ou ejaculação precoce.</t>
+  </si>
+  <si>
     <t>couve</t>
   </si>
   <si>
@@ -1758,6 +1779,9 @@
     <t>Transforma a fleuma (catarro); Refresca / clareia o calor; Diurético; Nutre o Yin</t>
   </si>
   <si>
+    <t>Atenção: Natureza fria: evitar na gravidez.</t>
+  </si>
+  <si>
     <t>aspargo</t>
   </si>
   <si>
@@ -1770,6 +1794,9 @@
     <t>Nutre o Yin; Refresca / clareia o calor; Diurético</t>
   </si>
   <si>
+    <t>Atenção: Não usar todo dia em quem tem frio; evitar em quadros de frio.</t>
+  </si>
+  <si>
     <t>vagem</t>
   </si>
   <si>
@@ -1791,6 +1818,9 @@
     <t>Pimentão</t>
   </si>
   <si>
+    <t>Quente</t>
+  </si>
+  <si>
     <t>maca</t>
   </si>
   <si>
@@ -1902,6 +1932,9 @@
     <t>Nutre o Yin; Faz descer o Qi do Estômago (náusea, refluxo); Diurético</t>
   </si>
   <si>
+    <t>Atenção: Pode piorar resfriado, indigestão e convalescença; pode dar coceira na pele.</t>
+  </si>
+  <si>
     <t>uva</t>
   </si>
   <si>
@@ -2094,15 +2127,15 @@
     <t>Tonifica o Qi; Nutre o Sangue (Xue)</t>
   </si>
   <si>
+    <t>Atenção: Com moderação (no máximo 1 vez por semana), alternando as proteínas.</t>
+  </si>
+  <si>
     <t>carne-de-cordeiro</t>
   </si>
   <si>
     <t>Carne de cordeiro</t>
   </si>
   <si>
-    <t>Quente</t>
-  </si>
-  <si>
     <t>Aquece/tonifica o Yang; Aquece o interior / dispersa o frio</t>
   </si>
   <si>
@@ -2160,6 +2193,9 @@
     <t>Aquece/tonifica o Yang</t>
   </si>
   <si>
+    <t>Atenção: Evitar na ejaculação precoce; em excesso favorece supurações.</t>
+  </si>
+  <si>
     <t>ostra-e-mariscos</t>
   </si>
   <si>
@@ -2172,6 +2208,9 @@
     <t>Nutre o Yin; Nutre o Sangue (Xue); Acalma o Shen (mente); Acalma o vento / faz descer o Yang do Fígado</t>
   </si>
   <si>
+    <t>Atenção: natureza fria nos livros de referência; cozida, fica mais suave.</t>
+  </si>
+  <si>
     <t>ovo</t>
   </si>
   <si>
@@ -2184,6 +2223,9 @@
     <t>Nutre o Yin; Nutre o Sangue (Xue); Acalma o Shen (mente); Umedece a secura</t>
   </si>
   <si>
+    <t>Atenção: Com moderação (2 a 3 vezes por semana).</t>
+  </si>
+  <si>
     <t>pato</t>
   </si>
   <si>
@@ -2226,6 +2268,9 @@
     <t>Queijo</t>
   </si>
   <si>
+    <t>Atenção: Ruim para digestão fraca; gera umidade.</t>
+  </si>
+  <si>
     <t>manteiga-e-ghee</t>
   </si>
   <si>
@@ -2289,6 +2334,9 @@
     <t>Nutre o Sangue (Xue); Nutre o Yin; Nutre a Essência (Jing); Umedece os intestinos (laxante suave)</t>
   </si>
   <si>
+    <t>Atenção: Evitar com intestino solto.</t>
+  </si>
+  <si>
     <t>semente-de-abobora</t>
   </si>
   <si>
@@ -2313,6 +2361,9 @@
     <t>Tonifica o Qi; Umedece a secura</t>
   </si>
   <si>
+    <t>Atenção: Preferir cozido em água com sal, não torrado.</t>
+  </si>
+  <si>
     <t>linhaca</t>
   </si>
   <si>
@@ -2346,6 +2397,9 @@
     <t>Aquece o interior / dispersa o frio; Antiparasitário; Move o Qi</t>
   </si>
   <si>
+    <t>Atenção: Pode piorar problemas de olhos, dentes, língua e garganta.</t>
+  </si>
+  <si>
     <t>cebolinha</t>
   </si>
   <si>
@@ -2367,6 +2421,9 @@
     <t>Libera o exterior (vento-frio); Aquece o interior / dispersa o frio; Faz descer o Qi do Estômago (náusea, refluxo)</t>
   </si>
   <si>
+    <t>Atenção: Evitar na hipertensão, gastrite e alergias (aumenta o calor interno).</t>
+  </si>
+  <si>
     <t>gengibre-seco</t>
   </si>
   <si>
@@ -2433,6 +2490,9 @@
     <t>Aquece o interior / dispersa o frio; Ajuda a digestão / dissolve alimentos retidos</t>
   </si>
   <si>
+    <t>Atenção: Evitar em pessoas agitadas ou com calor interno, secura e irritação.</t>
+  </si>
+  <si>
     <t>pimenta-vermelha</t>
   </si>
   <si>
@@ -2553,6 +2613,9 @@
     <t>Umedece a secura; Tonifica o Qi; Umedece os intestinos (laxante suave)</t>
   </si>
   <si>
+    <t>Atenção: Evitar com reumatismo, diarreia ou muito catarro.</t>
+  </si>
+  <si>
     <t>acucar-mascavo</t>
   </si>
   <si>
@@ -2562,7 +2625,7 @@
     <t>Move o Sangue; Aquece o interior / dispersa o frio</t>
   </si>
   <si>
-    <t>Com moderação.</t>
+    <t>Com moderação. Atenção: Aumenta o catarro.</t>
   </si>
   <si>
     <t>cabelo-de-milho-cha</t>
@@ -3038,7 +3101,7 @@
     <t xml:space="preserve">5 rodelas de gengibre fresco [Gengibre fresco]
 1 pau de canela [Canela]
 500 ml de água
-(opcional) 1 colher (chá) de açúcar mascavo [Açúcar mascavo]</t>
+(opcional) 1 colher (chá) de açúcar mascavo (omita se houver catarro) [Açúcar mascavo]</t>
   </si>
   <si>
     <t xml:space="preserve">Coloque a água, o gengibre e a canela numa panela.
@@ -3177,7 +3240,7 @@
   <si>
     <t xml:space="preserve">2 peras [Pera]
 10 amêndoas [Amêndoa]
-(opcional) 2 colheres (chá) de mel [Mel]
+(opcional) 2 colheres (chá) de mel (omita se houver catarro) [Mel]
 2 xícaras (chá) de água</t>
   </si>
   <si>
@@ -3370,7 +3433,7 @@
   <si>
     <t xml:space="preserve">1 xícara (chá) de feijão-mungo (o grão verde do moyashi) [Feijão-mungo (moyashi)]
 1,5 litro de água
-(opcional) 1 colher (sopa) de mel [Mel]</t>
+(opcional) 1 colher (sopa) de mel (omita se houver catarro) [Mel]</t>
   </si>
   <si>
     <t xml:space="preserve">Lave o feijão-mungo e cozinhe na água em fogo médio por 40 a 50 minutos, até os grãos abrirem.
@@ -3754,7 +3817,7 @@
     <t xml:space="preserve">5 rodelas de gengibre fresco [Gengibre fresco]
 A parte branca de 3 talos de cebolinha [Cebolinha]
 500 ml de água
-(opcional) 1 colher (chá) de açúcar mascavo [Açúcar mascavo]</t>
+(opcional) 1 colher (chá) de açúcar mascavo (omita se houver catarro) [Açúcar mascavo]</t>
   </si>
   <si>
     <t xml:space="preserve">Ferva o gengibre na água por 5 minutos.
@@ -6548,7 +6611,7 @@
         <v>388</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>390</v>
@@ -6557,10 +6620,10 @@
         <v>287</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>1</v>
@@ -6577,10 +6640,10 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>388</v>
@@ -6595,10 +6658,10 @@
         <v>287</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>1</v>
@@ -6615,16 +6678,16 @@
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>388</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>414</v>
@@ -6662,7 +6725,7 @@
         <v>388</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>414</v>
@@ -6700,7 +6763,7 @@
         <v>388</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>390</v>
@@ -6738,7 +6801,7 @@
         <v>388</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>390</v>
@@ -6756,7 +6819,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>1</v>
+        <v>430</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>42</v>
@@ -6767,10 +6830,10 @@
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>388</v>
@@ -6779,22 +6842,22 @@
         <v>400</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>42</v>
@@ -6805,10 +6868,10 @@
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>388</v>
@@ -6817,16 +6880,16 @@
         <v>389</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>1</v>
@@ -6843,10 +6906,10 @@
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>388</v>
@@ -6867,10 +6930,10 @@
         <v>1</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>42</v>
@@ -6881,34 +6944,34 @@
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>1</v>
+        <v>451</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>42</v>
@@ -6919,13 +6982,13 @@
     </row>
     <row r="15" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>400</v>
@@ -6937,10 +7000,10 @@
         <v>287</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>1</v>
@@ -6957,13 +7020,13 @@
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>389</v>
@@ -6975,7 +7038,7 @@
         <v>287</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>397</v>
@@ -6984,7 +7047,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>42</v>
@@ -6995,16 +7058,16 @@
     </row>
     <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>390</v>
@@ -7013,10 +7076,10 @@
         <v>287</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>1</v>
@@ -7033,16 +7096,16 @@
     </row>
     <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>390</v>
@@ -7051,10 +7114,10 @@
         <v>287</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>1</v>
@@ -7071,16 +7134,16 @@
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>390</v>
@@ -7092,13 +7155,13 @@
         <v>428</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>1</v>
+        <v>470</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>42</v>
@@ -7109,13 +7172,13 @@
     </row>
     <row r="20" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>389</v>
@@ -7127,10 +7190,10 @@
         <v>287</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>1</v>
@@ -7147,13 +7210,13 @@
     </row>
     <row r="21" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>389</v>
@@ -7165,10 +7228,10 @@
         <v>287</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>1</v>
@@ -7185,13 +7248,13 @@
     </row>
     <row r="22" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>389</v>
@@ -7206,7 +7269,7 @@
         <v>391</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>1</v>
@@ -7223,13 +7286,13 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>389</v>
@@ -7261,13 +7324,13 @@
     </row>
     <row r="24" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>400</v>
@@ -7282,7 +7345,7 @@
         <v>391</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I24" s="4" t="s">
         <v>1</v>
@@ -7299,13 +7362,13 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>389</v>
@@ -7320,7 +7383,7 @@
         <v>415</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="I25" s="4" t="s">
         <v>1</v>
@@ -7337,13 +7400,13 @@
     </row>
     <row r="26" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>389</v>
@@ -7358,7 +7421,7 @@
         <v>391</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I26" s="4" t="s">
         <v>1</v>
@@ -7375,13 +7438,13 @@
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>389</v>
@@ -7393,16 +7456,16 @@
         <v>287</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I27" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>42</v>
@@ -7413,13 +7476,13 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>389</v>
@@ -7434,13 +7497,13 @@
         <v>391</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>42</v>
@@ -7451,13 +7514,13 @@
     </row>
     <row r="29" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>389</v>
@@ -7472,13 +7535,13 @@
         <v>391</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I29" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>42</v>
@@ -7489,13 +7552,13 @@
     </row>
     <row r="30" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>389</v>
@@ -7507,10 +7570,10 @@
         <v>287</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="I30" s="4" t="s">
         <v>1</v>
@@ -7527,13 +7590,13 @@
     </row>
     <row r="31" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>389</v>
@@ -7545,10 +7608,10 @@
         <v>287</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I31" s="4" t="s">
         <v>1</v>
@@ -7565,16 +7628,16 @@
     </row>
     <row r="32" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>390</v>
@@ -7586,13 +7649,13 @@
         <v>391</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>42</v>
@@ -7603,16 +7666,16 @@
     </row>
     <row r="33" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>390</v>
@@ -7621,10 +7684,10 @@
         <v>287</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="I33" s="4" t="s">
         <v>1</v>
@@ -7641,16 +7704,16 @@
     </row>
     <row r="34" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>390</v>
@@ -7662,13 +7725,13 @@
         <v>428</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="I34" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>1</v>
+        <v>517</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>42</v>
@@ -7679,34 +7742,34 @@
     </row>
     <row r="35" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="I35" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>1</v>
+        <v>522</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>42</v>
@@ -7717,16 +7780,16 @@
     </row>
     <row r="36" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>390</v>
@@ -7738,7 +7801,7 @@
         <v>428</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="I36" s="4" t="s">
         <v>1</v>
@@ -7755,28 +7818,28 @@
     </row>
     <row r="37" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="I37" s="4" t="s">
         <v>1</v>
@@ -7793,34 +7856,34 @@
     </row>
     <row r="38" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I38" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>1</v>
+        <v>534</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>42</v>
@@ -7831,28 +7894,28 @@
     </row>
     <row r="39" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="I39" s="4" t="s">
         <v>1</v>
@@ -7869,34 +7932,34 @@
     </row>
     <row r="40" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="I40" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>42</v>
@@ -7907,34 +7970,34 @@
     </row>
     <row r="41" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>42</v>
@@ -7945,16 +8008,16 @@
     </row>
     <row r="42" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>390</v>
@@ -7963,16 +8026,16 @@
         <v>287</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="I42" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>1</v>
+        <v>549</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>42</v>
@@ -7983,28 +8046,28 @@
     </row>
     <row r="43" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>1</v>
@@ -8021,28 +8084,28 @@
     </row>
     <row r="44" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>1</v>
@@ -8059,16 +8122,16 @@
     </row>
     <row r="45" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>390</v>
@@ -8077,10 +8140,10 @@
         <v>287</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="I45" s="4" t="s">
         <v>1</v>
@@ -8097,28 +8160,28 @@
     </row>
     <row r="46" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="I46" s="4" t="s">
         <v>1</v>
@@ -8135,16 +8198,16 @@
     </row>
     <row r="47" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>390</v>
@@ -8153,10 +8216,10 @@
         <v>287</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="I47" s="4" t="s">
         <v>1</v>
@@ -8173,34 +8236,34 @@
     </row>
     <row r="48" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="I48" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J48" s="5" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>42</v>
@@ -8211,28 +8274,28 @@
     </row>
     <row r="49" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>567</v>
+        <v>574</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>1</v>
@@ -8249,28 +8312,28 @@
     </row>
     <row r="50" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>568</v>
+        <v>575</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="H50" s="5" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>1</v>
@@ -8287,13 +8350,13 @@
     </row>
     <row r="51" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>389</v>
@@ -8305,10 +8368,10 @@
         <v>287</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="H51" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I51" s="4" t="s">
         <v>1</v>
@@ -8325,34 +8388,34 @@
     </row>
     <row r="52" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J52" s="5" t="s">
-        <v>1</v>
+        <v>587</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>42</v>
@@ -8363,34 +8426,34 @@
     </row>
     <row r="53" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>42</v>
@@ -8401,13 +8464,13 @@
     </row>
     <row r="54" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>389</v>
@@ -8419,10 +8482,10 @@
         <v>287</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H54" s="5" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>1</v>
@@ -8439,16 +8502,16 @@
     </row>
     <row r="55" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>390</v>
@@ -8457,16 +8520,16 @@
         <v>287</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J55" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>42</v>
@@ -8477,19 +8540,19 @@
     </row>
     <row r="56" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>220</v>
@@ -8515,28 +8578,28 @@
     </row>
     <row r="57" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="I57" s="4" t="s">
         <v>1</v>
@@ -8553,16 +8616,16 @@
     </row>
     <row r="58" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>390</v>
@@ -8571,10 +8634,10 @@
         <v>287</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>1</v>
@@ -8591,16 +8654,16 @@
     </row>
     <row r="59" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>390</v>
@@ -8609,10 +8672,10 @@
         <v>287</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>1</v>
@@ -8629,16 +8692,16 @@
     </row>
     <row r="60" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="B60" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="D60" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>390</v>
@@ -8647,10 +8710,10 @@
         <v>287</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>1</v>
@@ -8667,16 +8730,16 @@
     </row>
     <row r="61" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>459</v>
+        <v>405</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>390</v>
@@ -8685,10 +8748,10 @@
         <v>287</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>1</v>
@@ -8705,28 +8768,28 @@
     </row>
     <row r="62" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H62" s="5" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="I62" s="4" t="s">
         <v>1</v>
@@ -8743,28 +8806,28 @@
     </row>
     <row r="63" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
       <c r="I63" s="4" t="s">
         <v>1</v>
@@ -8781,28 +8844,28 @@
     </row>
     <row r="64" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="H64" s="5" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
       <c r="I64" s="4" t="s">
         <v>1</v>
@@ -8819,28 +8882,28 @@
     </row>
     <row r="65" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>618</v>
+        <v>628</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>619</v>
+        <v>629</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>621</v>
+        <v>631</v>
       </c>
       <c r="I65" s="4" t="s">
         <v>1</v>
@@ -8857,13 +8920,13 @@
     </row>
     <row r="66" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>622</v>
+        <v>632</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>623</v>
+        <v>633</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>389</v>
@@ -8875,10 +8938,10 @@
         <v>287</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="H66" s="5" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="I66" s="4" t="s">
         <v>1</v>
@@ -8895,34 +8958,34 @@
     </row>
     <row r="67" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>626</v>
+        <v>636</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>413</v>
+        <v>461</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>627</v>
+        <v>637</v>
       </c>
       <c r="I67" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J67" s="5" t="s">
-        <v>1</v>
+        <v>638</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>42</v>
@@ -8933,28 +8996,28 @@
     </row>
     <row r="68" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="H68" s="5" t="s">
-        <v>631</v>
+        <v>642</v>
       </c>
       <c r="I68" s="4" t="s">
         <v>1</v>
@@ -8971,13 +9034,13 @@
     </row>
     <row r="69" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>632</v>
+        <v>643</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>389</v>
@@ -8989,10 +9052,10 @@
         <v>287</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>1</v>
@@ -9009,28 +9072,28 @@
     </row>
     <row r="70" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="H70" s="5" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="I70" s="4" t="s">
         <v>1</v>
@@ -9047,28 +9110,28 @@
     </row>
     <row r="71" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="H71" s="5" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="I71" s="4" t="s">
         <v>1</v>
@@ -9085,16 +9148,16 @@
     </row>
     <row r="72" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>390</v>
@@ -9103,10 +9166,10 @@
         <v>287</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H72" s="5" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="I72" s="4" t="s">
         <v>1</v>
@@ -9123,28 +9186,28 @@
     </row>
     <row r="73" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="I73" s="4" t="s">
         <v>1</v>
@@ -9161,13 +9224,13 @@
     </row>
     <row r="74" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>400</v>
@@ -9179,10 +9242,10 @@
         <v>287</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H74" s="5" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="I74" s="4" t="s">
         <v>1</v>
@@ -9199,13 +9262,13 @@
     </row>
     <row r="75" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>400</v>
@@ -9220,13 +9283,13 @@
         <v>391</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>42</v>
@@ -9237,13 +9300,13 @@
     </row>
     <row r="76" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>389</v>
@@ -9255,10 +9318,10 @@
         <v>287</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="H76" s="5" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>1</v>
@@ -9275,16 +9338,16 @@
     </row>
     <row r="77" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>390</v>
@@ -9293,10 +9356,10 @@
         <v>287</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>1</v>
@@ -9313,19 +9376,19 @@
     </row>
     <row r="78" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>287</v>
@@ -9334,13 +9397,13 @@
         <v>428</v>
       </c>
       <c r="H78" s="5" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="I78" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J78" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>42</v>
@@ -9351,34 +9414,34 @@
     </row>
     <row r="79" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H79" s="5" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="I79" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J79" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>42</v>
@@ -9389,28 +9452,28 @@
     </row>
     <row r="80" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
       <c r="H80" s="5" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="I80" s="4" t="s">
         <v>1</v>
@@ -9427,13 +9490,13 @@
     </row>
     <row r="81" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>389</v>
@@ -9445,10 +9508,10 @@
         <v>287</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="H81" s="5" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="I81" s="4" t="s">
         <v>1</v>
@@ -9465,28 +9528,28 @@
     </row>
     <row r="82" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="H82" s="5" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="I82" s="4" t="s">
         <v>1</v>
@@ -9503,28 +9566,28 @@
     </row>
     <row r="83" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="I83" s="4" t="s">
         <v>1</v>
@@ -9541,13 +9604,13 @@
     </row>
     <row r="84" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>400</v>
@@ -9562,7 +9625,7 @@
         <v>391</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="I84" s="4" t="s">
         <v>1</v>
@@ -9579,16 +9642,16 @@
     </row>
     <row r="85" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>390</v>
@@ -9600,13 +9663,13 @@
         <v>391</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="I85" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J85" s="5" t="s">
-        <v>1</v>
+        <v>703</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>42</v>
@@ -9617,16 +9680,16 @@
     </row>
     <row r="86" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>390</v>
@@ -9635,13 +9698,13 @@
         <v>287</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>1</v>
@@ -9655,16 +9718,16 @@
     </row>
     <row r="87" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>414</v>
@@ -9676,13 +9739,13 @@
         <v>415</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J87" s="5" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>42</v>
@@ -9693,28 +9756,28 @@
     </row>
     <row r="88" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="I88" s="4" t="s">
         <v>1</v>
@@ -9731,13 +9794,13 @@
     </row>
     <row r="89" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>389</v>
@@ -9758,7 +9821,7 @@
         <v>1</v>
       </c>
       <c r="J89" s="5" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>42</v>
@@ -9769,13 +9832,13 @@
     </row>
     <row r="90" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>400</v>
@@ -9787,16 +9850,16 @@
         <v>287</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="I90" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J90" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>42</v>
@@ -9807,13 +9870,13 @@
     </row>
     <row r="91" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>400</v>
@@ -9825,16 +9888,16 @@
         <v>287</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J91" s="5" t="s">
-        <v>1</v>
+        <v>725</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>42</v>
@@ -9845,34 +9908,34 @@
     </row>
     <row r="92" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J92" s="5" t="s">
-        <v>1</v>
+        <v>730</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>42</v>
@@ -9883,13 +9946,13 @@
     </row>
     <row r="93" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>389</v>
@@ -9901,16 +9964,16 @@
         <v>287</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>720</v>
+        <v>733</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>721</v>
+        <v>734</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>1</v>
+        <v>735</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>42</v>
@@ -9921,16 +9984,16 @@
     </row>
     <row r="94" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>723</v>
+        <v>737</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>414</v>
@@ -9939,10 +10002,10 @@
         <v>287</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>582</v>
+        <v>590</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>1</v>
@@ -9959,34 +10022,34 @@
     </row>
     <row r="95" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F95" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>727</v>
+        <v>741</v>
       </c>
       <c r="I95" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J95" s="5" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>42</v>
@@ -9997,13 +10060,13 @@
     </row>
     <row r="96" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>729</v>
+        <v>743</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>730</v>
+        <v>744</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>389</v>
@@ -10015,13 +10078,13 @@
         <v>287</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>1</v>
@@ -10035,31 +10098,31 @@
     </row>
     <row r="97" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>732</v>
+        <v>746</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>733</v>
+        <v>747</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F97" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>1</v>
@@ -10073,13 +10136,13 @@
     </row>
     <row r="98" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>735</v>
+        <v>749</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>389</v>
@@ -10097,10 +10160,10 @@
         <v>1</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J98" s="5" t="s">
-        <v>1</v>
+        <v>750</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>42</v>
@@ -10111,13 +10174,13 @@
     </row>
     <row r="99" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>731</v>
+        <v>745</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>400</v>
@@ -10132,13 +10195,13 @@
         <v>391</v>
       </c>
       <c r="H99" s="5" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>42</v>
@@ -10149,13 +10212,13 @@
     </row>
     <row r="100" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>400</v>
@@ -10167,10 +10230,10 @@
         <v>287</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="H100" s="5" t="s">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>1</v>
@@ -10187,13 +10250,13 @@
     </row>
     <row r="101" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>400</v>
@@ -10208,7 +10271,7 @@
         <v>415</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="I101" s="4" t="s">
         <v>1</v>
@@ -10225,13 +10288,13 @@
     </row>
     <row r="102" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>400</v>
@@ -10243,16 +10306,16 @@
         <v>287</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="H102" s="5" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J102" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>42</v>
@@ -10263,13 +10326,13 @@
     </row>
     <row r="103" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>389</v>
@@ -10281,10 +10344,10 @@
         <v>287</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="H103" s="5" t="s">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>1</v>
@@ -10301,13 +10364,13 @@
     </row>
     <row r="104" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>389</v>
@@ -10319,16 +10382,16 @@
         <v>287</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="H104" s="5" t="s">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J104" s="5" t="s">
-        <v>1</v>
+        <v>772</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>42</v>
@@ -10339,13 +10402,13 @@
     </row>
     <row r="105" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>757</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>758</v>
-      </c>
-      <c r="C105" s="4" t="s">
-        <v>742</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>389</v>
@@ -10357,10 +10420,10 @@
         <v>287</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>759</v>
+        <v>775</v>
       </c>
       <c r="H105" s="5" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>1</v>
@@ -10377,13 +10440,13 @@
     </row>
     <row r="106" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>761</v>
+        <v>777</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>762</v>
+        <v>778</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>389</v>
@@ -10395,16 +10458,16 @@
         <v>287</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="H106" s="5" t="s">
-        <v>764</v>
+        <v>780</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J106" s="5" t="s">
-        <v>1</v>
+        <v>781</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>42</v>
@@ -10415,13 +10478,13 @@
     </row>
     <row r="107" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>389</v>
@@ -10433,10 +10496,10 @@
         <v>287</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="I107" s="4" t="s">
         <v>1</v>
@@ -10453,13 +10516,13 @@
     </row>
     <row r="108" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>389</v>
@@ -10471,10 +10534,10 @@
         <v>287</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
       <c r="I108" s="4" t="s">
         <v>1</v>
@@ -10491,19 +10554,19 @@
     </row>
     <row r="109" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>694</v>
+        <v>400</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>220</v>
@@ -10512,13 +10575,13 @@
         <v>396</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J109" s="5" t="s">
-        <v>1</v>
+        <v>793</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>42</v>
@@ -10529,28 +10592,28 @@
     </row>
     <row r="110" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>776</v>
+        <v>794</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>777</v>
+        <v>795</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F110" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c r="H110" s="5" t="s">
-        <v>778</v>
+        <v>796</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>1</v>
@@ -10567,34 +10630,34 @@
     </row>
     <row r="111" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F111" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>782</v>
+        <v>800</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J111" s="5" t="s">
-        <v>1</v>
+        <v>801</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>42</v>
@@ -10605,34 +10668,34 @@
     </row>
     <row r="112" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>784</v>
+        <v>803</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F112" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>786</v>
+        <v>805</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>1</v>
+        <v>801</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>42</v>
@@ -10643,34 +10706,34 @@
     </row>
     <row r="113" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>787</v>
+        <v>806</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>788</v>
+        <v>807</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="F113" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>763</v>
+        <v>779</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>790</v>
+        <v>809</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J113" s="5" t="s">
-        <v>791</v>
+        <v>810</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>42</v>
@@ -10681,31 +10744,31 @@
     </row>
     <row r="114" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>792</v>
+        <v>811</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>793</v>
+        <v>812</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="F114" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>794</v>
+        <v>813</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>1</v>
@@ -10719,19 +10782,19 @@
     </row>
     <row r="115" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>795</v>
+        <v>814</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>796</v>
+        <v>815</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F115" s="4" t="s">
         <v>220</v>
@@ -10740,7 +10803,7 @@
         <v>415</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>797</v>
+        <v>816</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>1</v>
@@ -10757,28 +10820,28 @@
     </row>
     <row r="116" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>798</v>
+        <v>817</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>799</v>
+        <v>818</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F116" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>800</v>
+        <v>819</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>1</v>
@@ -10795,34 +10858,34 @@
     </row>
     <row r="117" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>802</v>
+        <v>821</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>803</v>
+        <v>822</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F117" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J117" s="5" t="s">
-        <v>1</v>
+        <v>824</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>42</v>
@@ -10833,34 +10896,34 @@
     </row>
     <row r="118" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F118" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="J118" s="5" t="s">
-        <v>1</v>
+        <v>824</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>42</v>
@@ -10871,28 +10934,28 @@
     </row>
     <row r="119" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="F119" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="H119" s="5" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>1</v>
@@ -10909,28 +10972,28 @@
     </row>
     <row r="120" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F120" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>1</v>
@@ -10947,28 +11010,28 @@
     </row>
     <row r="121" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F121" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>781</v>
+        <v>799</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>1</v>
@@ -10985,34 +11048,34 @@
     </row>
     <row r="122" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F122" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="H122" s="5" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="I122" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J122" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>42</v>
@@ -11023,28 +11086,28 @@
     </row>
     <row r="123" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F123" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="I123" s="4" t="s">
         <v>1</v>
@@ -11061,28 +11124,28 @@
     </row>
     <row r="124" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F124" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="H124" s="5" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="I124" s="4" t="s">
         <v>1</v>
@@ -11099,19 +11162,19 @@
     </row>
     <row r="125" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F125" s="4" t="s">
         <v>220</v>
@@ -11120,7 +11183,7 @@
         <v>391</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>804</v>
+        <v>823</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>1</v>
@@ -11137,28 +11200,28 @@
     </row>
     <row r="126" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F126" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>1</v>
@@ -11175,19 +11238,19 @@
     </row>
     <row r="127" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>220</v>
@@ -11196,7 +11259,7 @@
         <v>391</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="I127" s="4" t="s">
         <v>1</v>
@@ -11213,34 +11276,34 @@
     </row>
     <row r="128" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="F128" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="H128" s="5" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J128" s="5" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>42</v>
@@ -11251,13 +11314,13 @@
     </row>
     <row r="129" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>389</v>
@@ -11269,16 +11332,16 @@
         <v>287</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
       <c r="H129" s="5" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="I129" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J129" s="5" t="s">
-        <v>1</v>
+        <v>865</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>42</v>
@@ -11289,13 +11352,13 @@
     </row>
     <row r="130" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>845</v>
+        <v>866</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>846</v>
+        <v>867</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>400</v>
@@ -11307,16 +11370,16 @@
         <v>287</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="I130" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J130" s="5" t="s">
-        <v>848</v>
+        <v>869</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>42</v>
@@ -11327,13 +11390,13 @@
     </row>
     <row r="131" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>849</v>
+        <v>870</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>850</v>
+        <v>871</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>389</v>
@@ -11345,16 +11408,16 @@
         <v>287</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="I131" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J131" s="5" t="s">
-        <v>854</v>
+        <v>875</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>42</v>
@@ -11365,28 +11428,28 @@
     </row>
     <row r="132" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>856</v>
+        <v>877</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F132" s="4" t="s">
         <v>287</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="H132" s="5" t="s">
-        <v>857</v>
+        <v>878</v>
       </c>
       <c r="I132" s="4" t="s">
         <v>1</v>
@@ -11403,31 +11466,31 @@
     </row>
     <row r="133" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>858</v>
+        <v>879</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>859</v>
+        <v>880</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="F133" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>860</v>
+        <v>881</v>
       </c>
       <c r="H133" s="5" t="s">
-        <v>861</v>
+        <v>882</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="J133" s="5" t="s">
         <v>1</v>
@@ -11441,34 +11504,34 @@
     </row>
     <row r="134" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>863</v>
+        <v>884</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>864</v>
+        <v>885</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D134" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F134" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>865</v>
+        <v>886</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J134" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>42</v>
@@ -11479,16 +11542,16 @@
     </row>
     <row r="135" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>867</v>
+        <v>888</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>390</v>
@@ -11497,16 +11560,16 @@
         <v>287</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>868</v>
+        <v>889</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>1</v>
       </c>
       <c r="J135" s="5" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>42</v>
@@ -11517,31 +11580,31 @@
     </row>
     <row r="136" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>869</v>
+        <v>890</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>870</v>
+        <v>891</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D136" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="H136" s="5" t="s">
         <v>1</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>872</v>
+        <v>893</v>
       </c>
       <c r="J136" s="5" t="s">
         <v>1</v>
@@ -11555,31 +11618,31 @@
     </row>
     <row r="137" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>874</v>
+        <v>895</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>851</v>
+        <v>872</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>789</v>
+        <v>808</v>
       </c>
       <c r="F137" s="4" t="s">
         <v>220</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>875</v>
+        <v>896</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>1</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>876</v>
+        <v>897</v>
       </c>
       <c r="J137" s="5" t="s">
         <v>1</v>
@@ -11593,13 +11656,13 @@
     </row>
     <row r="138" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>877</v>
+        <v>898</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>878</v>
+        <v>899</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D138" s="4" t="s">
         <v>389</v>
@@ -11611,13 +11674,13 @@
         <v>287</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>1</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>1</v>
@@ -11631,16 +11694,16 @@
     </row>
     <row r="139" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>882</v>
+        <v>903</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>390</v>
@@ -11655,7 +11718,7 @@
         <v>1</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="J139" s="5" t="s">
         <v>1</v>
@@ -11669,19 +11732,19 @@
     </row>
     <row r="140" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>884</v>
+        <v>905</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>885</v>
+        <v>906</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F140" s="4" t="s">
         <v>35</v>
@@ -11693,10 +11756,10 @@
         <v>1</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>883</v>
+        <v>904</v>
       </c>
       <c r="J140" s="5" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>42</v>
@@ -11707,16 +11770,16 @@
     </row>
     <row r="141" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>887</v>
+        <v>908</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>390</v>
@@ -11731,7 +11794,7 @@
         <v>1</v>
       </c>
       <c r="I141" s="4" t="s">
-        <v>889</v>
+        <v>910</v>
       </c>
       <c r="J141" s="5" t="s">
         <v>1</v>
@@ -11745,16 +11808,16 @@
     </row>
     <row r="142" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>890</v>
+        <v>911</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>891</v>
+        <v>912</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>879</v>
+        <v>900</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E142" s="4" t="s">
         <v>390</v>
@@ -11769,10 +11832,10 @@
         <v>1</v>
       </c>
       <c r="I142" s="4" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="J142" s="5" t="s">
-        <v>893</v>
+        <v>914</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>42</v>
@@ -11858,22 +11921,22 @@
         <v>23</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>895</v>
+        <v>916</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>896</v>
+        <v>917</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>898</v>
+        <v>919</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>30</v>
@@ -11887,22 +11950,22 @@
         <v>160</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>899</v>
+        <v>920</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>900</v>
+        <v>921</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>901</v>
+        <v>922</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>902</v>
+        <v>923</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>903</v>
+        <v>924</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>904</v>
+        <v>925</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>42</v>
@@ -11916,22 +11979,22 @@
         <v>86</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>905</v>
+        <v>926</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>906</v>
+        <v>927</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>907</v>
+        <v>928</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>908</v>
+        <v>929</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>909</v>
+        <v>930</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>910</v>
+        <v>931</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>42</v>
@@ -11945,22 +12008,22 @@
         <v>287</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>911</v>
+        <v>932</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>912</v>
+        <v>933</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>913</v>
+        <v>934</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>914</v>
+        <v>935</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>915</v>
+        <v>936</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>916</v>
+        <v>937</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>42</v>
@@ -11974,22 +12037,22 @@
         <v>220</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>917</v>
+        <v>938</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>918</v>
+        <v>939</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>919</v>
+        <v>940</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>920</v>
+        <v>941</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>921</v>
+        <v>942</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>922</v>
+        <v>943</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>42</v>
@@ -12003,22 +12066,22 @@
         <v>35</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>923</v>
+        <v>944</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>924</v>
+        <v>945</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>925</v>
+        <v>946</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>926</v>
+        <v>947</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>927</v>
+        <v>948</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>928</v>
+        <v>949</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>42</v>
@@ -12066,28 +12129,28 @@
         <v>377</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>930</v>
+        <v>951</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>931</v>
+        <v>952</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>932</v>
+        <v>953</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>933</v>
+        <v>954</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>934</v>
+        <v>955</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>935</v>
+        <v>956</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>30</v>
@@ -12098,34 +12161,34 @@
     </row>
     <row r="2" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>936</v>
+        <v>957</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>937</v>
+        <v>958</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>941</v>
+        <v>962</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>942</v>
+        <v>963</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>943</v>
+        <v>964</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>944</v>
+        <v>965</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>42</v>
@@ -12136,34 +12199,34 @@
     </row>
     <row r="3" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>945</v>
+        <v>966</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>946</v>
+        <v>967</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>949</v>
+        <v>970</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>950</v>
+        <v>971</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>951</v>
+        <v>972</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>952</v>
+        <v>973</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>42</v>
@@ -12174,34 +12237,34 @@
     </row>
     <row r="4" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>953</v>
+        <v>974</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>954</v>
+        <v>975</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>958</v>
+        <v>979</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>959</v>
+        <v>980</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>960</v>
+        <v>981</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>961</v>
+        <v>982</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>42</v>
@@ -12212,34 +12275,34 @@
     </row>
     <row r="5" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>962</v>
+        <v>983</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>963</v>
+        <v>984</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>965</v>
+        <v>986</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>966</v>
+        <v>987</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>967</v>
+        <v>988</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>968</v>
+        <v>989</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>42</v>
@@ -12250,34 +12313,34 @@
     </row>
     <row r="6" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>970</v>
+        <v>991</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>974</v>
+        <v>995</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>975</v>
+        <v>996</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>976</v>
+        <v>997</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>977</v>
+        <v>998</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>42</v>
@@ -12288,34 +12351,34 @@
     </row>
     <row r="7" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>978</v>
+        <v>999</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>979</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>981</v>
+        <v>1002</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>982</v>
+        <v>1003</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>983</v>
+        <v>1004</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>984</v>
+        <v>1005</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>985</v>
+        <v>1006</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>42</v>
@@ -12326,34 +12389,34 @@
     </row>
     <row r="8" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>986</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>987</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>990</v>
+        <v>1011</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>991</v>
+        <v>1012</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>993</v>
+        <v>1014</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>42</v>
@@ -12364,34 +12427,34 @@
     </row>
     <row r="9" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>994</v>
+        <v>1015</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>995</v>
+        <v>1016</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>996</v>
+        <v>1017</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>997</v>
+        <v>1018</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>998</v>
+        <v>1019</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>999</v>
+        <v>1020</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>42</v>
@@ -12402,34 +12465,34 @@
     </row>
     <row r="10" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>1001</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>980</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>1004</v>
+        <v>1025</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>1005</v>
+        <v>1026</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>1006</v>
+        <v>1027</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>1007</v>
+        <v>1028</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>42</v>
@@ -12440,34 +12503,34 @@
     </row>
     <row r="11" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>1008</v>
+        <v>1029</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1009</v>
+        <v>1030</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1011</v>
+        <v>1032</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1012</v>
+        <v>1033</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>1013</v>
+        <v>1034</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1014</v>
+        <v>1035</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>42</v>
@@ -12478,34 +12541,34 @@
     </row>
     <row r="12" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>1015</v>
+        <v>1036</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1016</v>
+        <v>1037</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>1017</v>
+        <v>1038</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>1018</v>
+        <v>1039</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>1019</v>
+        <v>1040</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>1020</v>
+        <v>1041</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>42</v>
@@ -12516,34 +12579,34 @@
     </row>
     <row r="13" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>1021</v>
+        <v>1042</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1022</v>
+        <v>1043</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1023</v>
+        <v>1044</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>1024</v>
+        <v>1045</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>1025</v>
+        <v>1046</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>1026</v>
+        <v>1047</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>1027</v>
+        <v>1048</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>1028</v>
+        <v>1049</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>42</v>
@@ -12554,34 +12617,34 @@
     </row>
     <row r="14" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>1029</v>
+        <v>1050</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1030</v>
+        <v>1051</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>1031</v>
+        <v>1052</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>1032</v>
+        <v>1053</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>1033</v>
+        <v>1054</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>1034</v>
+        <v>1055</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>42</v>
@@ -12592,34 +12655,34 @@
     </row>
     <row r="15" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>1035</v>
+        <v>1056</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1036</v>
+        <v>1057</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1037</v>
+        <v>1058</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>1038</v>
+        <v>1059</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>1039</v>
+        <v>1060</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>1040</v>
+        <v>1061</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>42</v>
@@ -12630,34 +12693,34 @@
     </row>
     <row r="16" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>1041</v>
+        <v>1062</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1042</v>
+        <v>1063</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>1003</v>
+        <v>1024</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>1043</v>
+        <v>1064</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>1044</v>
+        <v>1065</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>1045</v>
+        <v>1066</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>1046</v>
+        <v>1067</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>42</v>
@@ -12668,34 +12731,34 @@
     </row>
     <row r="17" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>1047</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1048</v>
+        <v>1069</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1049</v>
+        <v>1070</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>1050</v>
+        <v>1071</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>1051</v>
+        <v>1072</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>1052</v>
+        <v>1073</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>42</v>
@@ -12706,34 +12769,34 @@
     </row>
     <row r="18" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>1053</v>
+        <v>1074</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1054</v>
+        <v>1075</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>1056</v>
+        <v>1077</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>1057</v>
+        <v>1078</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>1058</v>
+        <v>1079</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>1059</v>
+        <v>1080</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>42</v>
@@ -12744,34 +12807,34 @@
     </row>
     <row r="19" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>1060</v>
+        <v>1081</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1061</v>
+        <v>1082</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>940</v>
+        <v>961</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>1062</v>
+        <v>1083</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>1063</v>
+        <v>1084</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1064</v>
+        <v>1085</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>1065</v>
+        <v>1086</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>42</v>
@@ -12782,34 +12845,34 @@
     </row>
     <row r="20" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1067</v>
+        <v>1088</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>1068</v>
+        <v>1089</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>1069</v>
+        <v>1090</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>1070</v>
+        <v>1091</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>1071</v>
+        <v>1092</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>42</v>
@@ -12820,34 +12883,34 @@
     </row>
     <row r="21" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>1072</v>
+        <v>1093</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1073</v>
+        <v>1094</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>1074</v>
+        <v>1095</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>1075</v>
+        <v>1096</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>1076</v>
+        <v>1097</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>1077</v>
+        <v>1098</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>42</v>
@@ -12858,34 +12921,34 @@
     </row>
     <row r="22" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>1078</v>
+        <v>1099</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1079</v>
+        <v>1100</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>1080</v>
+        <v>1101</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>1081</v>
+        <v>1102</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>1082</v>
+        <v>1103</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>1083</v>
+        <v>1104</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>42</v>
@@ -12896,34 +12959,34 @@
     </row>
     <row r="23" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>1084</v>
+        <v>1105</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1085</v>
+        <v>1106</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>1086</v>
+        <v>1107</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>1087</v>
+        <v>1108</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>1088</v>
+        <v>1109</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>1089</v>
+        <v>1110</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>42</v>
@@ -12934,34 +12997,34 @@
     </row>
     <row r="24" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1091</v>
+        <v>1112</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1092</v>
+        <v>1113</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>1093</v>
+        <v>1114</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>1095</v>
+        <v>1116</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>1096</v>
+        <v>1117</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>1097</v>
+        <v>1118</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>1098</v>
+        <v>1119</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>42</v>
@@ -12972,34 +13035,34 @@
     </row>
     <row r="25" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>1099</v>
+        <v>1120</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1100</v>
+        <v>1121</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>1101</v>
+        <v>1122</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>1102</v>
+        <v>1123</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>1103</v>
+        <v>1124</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>1104</v>
+        <v>1125</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>42</v>
@@ -13010,34 +13073,34 @@
     </row>
     <row r="26" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>1105</v>
+        <v>1126</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1106</v>
+        <v>1127</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>1107</v>
+        <v>1128</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>1108</v>
+        <v>1129</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>1109</v>
+        <v>1130</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>1110</v>
+        <v>1131</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>1111</v>
+        <v>1132</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>42</v>
@@ -13048,34 +13111,34 @@
     </row>
     <row r="27" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>1112</v>
+        <v>1133</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1113</v>
+        <v>1134</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>1114</v>
+        <v>1135</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>1115</v>
+        <v>1136</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>1116</v>
+        <v>1137</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>1117</v>
+        <v>1138</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>1118</v>
+        <v>1139</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>42</v>
@@ -13086,34 +13149,34 @@
     </row>
     <row r="28" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>1119</v>
+        <v>1140</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1120</v>
+        <v>1141</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>980</v>
+        <v>1001</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>956</v>
+        <v>977</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>1121</v>
+        <v>1142</v>
       </c>
       <c r="H28" s="5" t="s">
-        <v>1122</v>
+        <v>1143</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>1123</v>
+        <v>1144</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>1124</v>
+        <v>1145</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>42</v>
@@ -13124,34 +13187,34 @@
     </row>
     <row r="29" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>1125</v>
+        <v>1146</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1126</v>
+        <v>1147</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>1127</v>
+        <v>1148</v>
       </c>
       <c r="H29" s="5" t="s">
-        <v>1128</v>
+        <v>1149</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>1129</v>
+        <v>1150</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>1130</v>
+        <v>1151</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>42</v>
@@ -13162,34 +13225,34 @@
     </row>
     <row r="30" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>1131</v>
+        <v>1152</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1132</v>
+        <v>1153</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>1133</v>
+        <v>1154</v>
       </c>
       <c r="H30" s="5" t="s">
-        <v>1134</v>
+        <v>1155</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>1135</v>
+        <v>1156</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>1136</v>
+        <v>1157</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>42</v>
@@ -13200,34 +13263,34 @@
     </row>
     <row r="31" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>1137</v>
+        <v>1158</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1138</v>
+        <v>1159</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>971</v>
+        <v>992</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>1010</v>
+        <v>1031</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>1139</v>
+        <v>1160</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>1140</v>
+        <v>1161</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>1141</v>
+        <v>1162</v>
       </c>
       <c r="J31" s="5" t="s">
-        <v>1142</v>
+        <v>1163</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>42</v>
@@ -13238,34 +13301,34 @@
     </row>
     <row r="32" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>1143</v>
+        <v>1164</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1144</v>
+        <v>1165</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>1145</v>
+        <v>1166</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>1146</v>
+        <v>1167</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>1147</v>
+        <v>1168</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>1148</v>
+        <v>1169</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>42</v>
@@ -13276,34 +13339,34 @@
     </row>
     <row r="33" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>1149</v>
+        <v>1170</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1150</v>
+        <v>1171</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>973</v>
+        <v>994</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>1151</v>
+        <v>1172</v>
       </c>
       <c r="H33" s="5" t="s">
-        <v>1152</v>
+        <v>1173</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>1153</v>
+        <v>1174</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>1154</v>
+        <v>1175</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>42</v>
@@ -13314,34 +13377,34 @@
     </row>
     <row r="34" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>1155</v>
+        <v>1176</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1156</v>
+        <v>1177</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>947</v>
+        <v>968</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>1094</v>
+        <v>1115</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>1158</v>
+        <v>1179</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>1159</v>
+        <v>1180</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>1160</v>
+        <v>1181</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>1161</v>
+        <v>1182</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>42</v>
@@ -13352,34 +13415,34 @@
     </row>
     <row r="35" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>1162</v>
+        <v>1183</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1163</v>
+        <v>1184</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>1164</v>
+        <v>1185</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>1165</v>
+        <v>1186</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>1166</v>
+        <v>1187</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>1167</v>
+        <v>1188</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>1168</v>
+        <v>1189</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>42</v>
@@ -13390,34 +13453,34 @@
     </row>
     <row r="36" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>1169</v>
+        <v>1190</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1170</v>
+        <v>1191</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>964</v>
+        <v>985</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>1171</v>
+        <v>1192</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>1172</v>
+        <v>1193</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>1173</v>
+        <v>1194</v>
       </c>
       <c r="J36" s="5" t="s">
-        <v>1174</v>
+        <v>1195</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>42</v>
@@ -13428,34 +13491,34 @@
     </row>
     <row r="37" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>1175</v>
+        <v>1196</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1176</v>
+        <v>1197</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>1177</v>
+        <v>1198</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>1178</v>
+        <v>1199</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>1179</v>
+        <v>1200</v>
       </c>
       <c r="J37" s="5" t="s">
-        <v>1180</v>
+        <v>1201</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>42</v>
@@ -13466,34 +13529,34 @@
     </row>
     <row r="38" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>1181</v>
+        <v>1202</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1182</v>
+        <v>1203</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>988</v>
+        <v>1009</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>989</v>
+        <v>1010</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>1055</v>
+        <v>1076</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>1183</v>
+        <v>1204</v>
       </c>
       <c r="H38" s="5" t="s">
-        <v>1184</v>
+        <v>1205</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>1185</v>
+        <v>1206</v>
       </c>
       <c r="J38" s="5" t="s">
-        <v>1186</v>
+        <v>1207</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>42</v>
@@ -13504,34 +13567,34 @@
     </row>
     <row r="39" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>1187</v>
+        <v>1208</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1188</v>
+        <v>1209</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>1024</v>
+        <v>1045</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>1189</v>
+        <v>1210</v>
       </c>
       <c r="H39" s="5" t="s">
-        <v>1190</v>
+        <v>1211</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>1191</v>
+        <v>1212</v>
       </c>
       <c r="J39" s="5" t="s">
-        <v>1192</v>
+        <v>1213</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>42</v>
@@ -13542,34 +13605,34 @@
     </row>
     <row r="40" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>1193</v>
+        <v>1214</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1194</v>
+        <v>1215</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>972</v>
+        <v>993</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>1195</v>
+        <v>1216</v>
       </c>
       <c r="H40" s="5" t="s">
-        <v>1196</v>
+        <v>1217</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>1197</v>
+        <v>1218</v>
       </c>
       <c r="J40" s="5" t="s">
-        <v>1198</v>
+        <v>1219</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>42</v>
@@ -13580,34 +13643,34 @@
     </row>
     <row r="41" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>1199</v>
+        <v>1220</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1200</v>
+        <v>1221</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>955</v>
+        <v>976</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>1201</v>
+        <v>1222</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>1202</v>
+        <v>1223</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>1203</v>
+        <v>1224</v>
       </c>
       <c r="H41" s="5" t="s">
-        <v>1204</v>
+        <v>1225</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>1205</v>
+        <v>1226</v>
       </c>
       <c r="J41" s="5" t="s">
-        <v>1206</v>
+        <v>1227</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>42</v>
@@ -13618,34 +13681,34 @@
     </row>
     <row r="42" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>1207</v>
+        <v>1228</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1208</v>
+        <v>1229</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>1157</v>
+        <v>1178</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>948</v>
+        <v>969</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>1209</v>
+        <v>1230</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>1210</v>
+        <v>1231</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>1211</v>
+        <v>1232</v>
       </c>
       <c r="J42" s="5" t="s">
-        <v>1212</v>
+        <v>1233</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>42</v>
@@ -13656,34 +13719,34 @@
     </row>
     <row r="43" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>1213</v>
+        <v>1234</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1214</v>
+        <v>1235</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>938</v>
+        <v>959</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>389</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>939</v>
+        <v>960</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>957</v>
+        <v>978</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>1215</v>
+        <v>1236</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>1216</v>
+        <v>1237</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>1217</v>
+        <v>1238</v>
       </c>
       <c r="J43" s="5" t="s">
-        <v>1218</v>
+        <v>1239</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>42</v>
@@ -13745,13 +13808,13 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>929</v>
+        <v>950</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1219</v>
+        <v>1240</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>1220</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13759,7 +13822,7 @@
         <v>379</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>694</v>
+        <v>600</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>1</v>
@@ -13792,7 +13855,7 @@
         <v>379</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>1</v>
@@ -13803,7 +13866,7 @@
         <v>379</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>1</v>
@@ -13811,57 +13874,57 @@
     </row>
     <row r="7" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>1221</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>1222</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="9" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>390</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1223</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="10" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1224</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="11" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>894</v>
+        <v>915</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1225</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="12" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13869,7 +13932,7 @@
         <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>159</v>
@@ -13880,7 +13943,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1226</v>
+        <v>1247</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>211</v>
@@ -13891,7 +13954,7 @@
         <v>22</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>871</v>
+        <v>892</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>85</v>
@@ -13902,7 +13965,7 @@
         <v>22</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1227</v>
+        <v>1248</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>144</v>
@@ -13913,10 +13976,10 @@
         <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1228</v>
+        <v>1249</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1229</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="17" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -13924,7 +13987,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>286</v>
@@ -13935,7 +13998,7 @@
         <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1230</v>
+        <v>1251</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>330</v>
@@ -13946,7 +14009,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1231</v>
+        <v>1252</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>235</v>
@@ -13957,7 +14020,7 @@
         <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1232</v>
+        <v>1253</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>219</v>
@@ -13968,7 +14031,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>53</v>
@@ -13979,7 +14042,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1233</v>
+        <v>1254</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>34</v>
@@ -13987,10 +14050,10 @@
     </row>
     <row r="23" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>1</v>
@@ -13998,10 +14061,10 @@
     </row>
     <row r="24" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>1</v>
@@ -14009,10 +14072,10 @@
     </row>
     <row r="25" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>724</v>
+        <v>738</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>1</v>
@@ -14020,10 +14083,10 @@
     </row>
     <row r="26" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>1</v>
@@ -14031,10 +14094,10 @@
     </row>
     <row r="27" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>1</v>
@@ -14042,10 +14105,10 @@
     </row>
     <row r="28" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1235</v>
+        <v>1256</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>1</v>
@@ -14053,10 +14116,10 @@
     </row>
     <row r="29" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1236</v>
+        <v>1257</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>1</v>
@@ -14064,10 +14127,10 @@
     </row>
     <row r="30" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1237</v>
+        <v>1258</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>1</v>
@@ -14075,10 +14138,10 @@
     </row>
     <row r="31" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1238</v>
+        <v>1259</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>1</v>
@@ -14086,10 +14149,10 @@
     </row>
     <row r="32" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1239</v>
+        <v>1260</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>1</v>
@@ -14097,10 +14160,10 @@
     </row>
     <row r="33" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1240</v>
+        <v>1261</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>1</v>
@@ -14108,10 +14171,10 @@
     </row>
     <row r="34" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>1</v>
@@ -14119,10 +14182,10 @@
     </row>
     <row r="35" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1241</v>
+        <v>1262</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>1</v>
@@ -14130,10 +14193,10 @@
     </row>
     <row r="36" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1242</v>
+        <v>1263</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>1</v>
@@ -14141,10 +14204,10 @@
     </row>
     <row r="37" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1243</v>
+        <v>1264</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>1</v>
@@ -14152,10 +14215,10 @@
     </row>
     <row r="38" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1244</v>
+        <v>1265</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>1</v>
@@ -14163,10 +14226,10 @@
     </row>
     <row r="39" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1245</v>
+        <v>1266</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>1</v>
@@ -14174,10 +14237,10 @@
     </row>
     <row r="40" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1246</v>
+        <v>1267</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>1</v>
@@ -14185,10 +14248,10 @@
     </row>
     <row r="41" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>760</v>
+        <v>776</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>1</v>
@@ -14196,10 +14259,10 @@
     </row>
     <row r="42" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1247</v>
+        <v>1268</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>1</v>
@@ -14207,10 +14270,10 @@
     </row>
     <row r="43" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1248</v>
+        <v>1269</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>1</v>
@@ -14218,10 +14281,10 @@
     </row>
     <row r="44" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>1234</v>
+        <v>1255</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1249</v>
+        <v>1270</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>1</v>
@@ -14229,57 +14292,57 @@
     </row>
     <row r="45" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="46" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="47" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>862</v>
+        <v>883</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="48" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1252</v>
+        <v>1273</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="49" spans="1:3" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>1250</v>
+        <v>1271</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>892</v>
+        <v>913</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1251</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
